--- a/Result/profitability/6592.xlsx
+++ b/Result/profitability/6592.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,6 +5129,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6592</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5758</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2220</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3539</v>
+      </c>
+      <c r="F38" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1182</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>20.52%</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>106</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1288</v>
+      </c>
+      <c r="K38" t="n">
+        <v>949</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.11125</v>
+      </c>
+      <c r="N38" t="n">
+        <v>60.16375</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.9473684210526316</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.3699999999999974</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.005985118084762209</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.02068965517241383</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.740000000000002</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.02914084742924139</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
